--- a/testcases/item-search/item-search-product-search-filters.xlsx
+++ b/testcases/item-search/item-search-product-search-filters.xlsx
@@ -52,7 +52,7 @@
     <t>Notes / Reason</t>
   </si>
   <si>
-    <t>TC-ISR-PRS-007</t>
+    <t>TC-ISR-PRF-001</t>
   </si>
   <si>
     <t>The Location dropdown lists offices</t>
@@ -111,7 +111,7 @@
     <t>The list closes without changing the selection</t>
   </si>
   <si>
-    <t>TC-ISR-PRS-008</t>
+    <t>TC-ISR-PRF-002</t>
   </si>
   <si>
     <t>The Region dropdown lists regions</t>
@@ -132,7 +132,7 @@
     <t>3. Press Escape</t>
   </si>
   <si>
-    <t>TC-ISR-PRS-009</t>
+    <t>TC-ISR-PRF-003</t>
   </si>
   <si>
     <t>Location and Region clear each other</t>
@@ -165,7 +165,7 @@
     <t>Location returns to the current office; Region clears</t>
   </si>
   <si>
-    <t>TC-ISR-PRS-010</t>
+    <t>TC-ISR-PRF-004</t>
   </si>
   <si>
     <t>The Product Organization popover offers the country checklist</t>
@@ -186,7 +186,7 @@
     <t>The popover closes with the selection unchanged ("None")</t>
   </si>
   <si>
-    <t>TC-ISR-PRS-011</t>
+    <t>TC-ISR-PRF-005</t>
   </si>
   <si>
     <t>The date fields open a calendar with a time spinner</t>
@@ -207,7 +207,7 @@
     <t>The popover closes; the field value is unchanged</t>
   </si>
   <si>
-    <t>TC-ISR-PRS-012</t>
+    <t>TC-ISR-PRF-006</t>
   </si>
   <si>
     <t>Quantity Greater Than Zero narrows the results</t>
@@ -231,7 +231,7 @@
     <t>The count returns to the unfiltered total</t>
   </si>
   <si>
-    <t>TC-ISR-PRS-020</t>
+    <t>TC-ISR-PRF-007</t>
   </si>
   <si>
     <t>A Prep date after the Return date is rejected with a message</t>
@@ -258,7 +258,7 @@
     <t>Both dates return to today's defaults and the message clears</t>
   </si>
   <si>
-    <t>TC-ISR-PRS-021</t>
+    <t>TC-ISR-PRF-008</t>
   </si>
   <si>
     <t>A date value renders fully inside its box in every month</t>
@@ -282,7 +282,7 @@
     <t>Both fields return to defaults</t>
   </si>
   <si>
-    <t>TC-ISR-PRS-031</t>
+    <t>TC-ISR-PRF-009</t>
   </si>
   <si>
     <t>The Active filter narrows the results to active products</t>
@@ -315,7 +315,7 @@
     <t>The result returns to the step 1 set — the added rows are gone again</t>
   </si>
   <si>
-    <t>TC-ISR-PRS-032</t>
+    <t>TC-ISR-PRF-010</t>
   </si>
   <si>
     <t>The Product Organization filter narrows the results and clearing it restores them</t>
